--- a/exports/purchase_orders_relationships.xlsx
+++ b/exports/purchase_orders_relationships.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6526797dc8a94865/Proyectos cursor/bsale-api-tools/exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_4B586D477F1A15CBC87514373F500E3E4507CFB5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E491E90A-005F-4A4A-B23E-22E685F7A79F}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_4B586D477F1A15CBC87514373F500E3E4507CFB5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8059B8D7-0A94-49FA-A8BC-A7BC1A6AC85C}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="78">
   <si>
     <t>oc_document_id</t>
   </si>
@@ -255,6 +255,13 @@
   <si>
     <t>totalAmount_relacionado_docs_unicos</t>
   </si>
+  <si>
+    <t>$env:PG_HOST="TU_HOST"
+$env:PG_DB="TU_DB"
+$env:PG_USER="TU_USER"
+$env:PG_PASSWORD="TU_PASSWORD"
+$env:PG_PORT="5432"</t>
+  </si>
 </sst>
 </file>
 
@@ -289,8 +296,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -40552,10 +40562,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.23046875" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="33.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="46.07421875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.4">
@@ -40638,6 +40649,11 @@
         <v>59086154</v>
       </c>
     </row>
+    <row r="17" spans="6:6" ht="72.900000000000006" x14ac:dyDescent="0.4">
+      <c r="F17" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/exports/purchase_orders_relationships.xlsx
+++ b/exports/purchase_orders_relationships.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/6526797dc8a94865/Proyectos cursor/bsale-api-tools/exports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_4B586D477F1A15CBC87514373F500E3E4507CFB5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8059B8D7-0A94-49FA-A8BC-A7BC1A6AC85C}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="11_4B586D477F1A15CBC87514373F500E3E4507CFB5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F9BD40E-D13B-4D72-9245-3C2A8C9225FE}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="11949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -256,10 +256,10 @@
     <t>totalAmount_relacionado_docs_unicos</t>
   </si>
   <si>
-    <t>$env:PG_HOST="TU_HOST"
-$env:PG_DB="TU_DB"
-$env:PG_USER="TU_USER"
-$env:PG_PASSWORD="TU_PASSWORD"
+    <t>$env:PG_HOST="vksg044wwo8kwoccogws44kk"
+$env:PG_DB="analytics"
+$env:PG_USER="postgres"
+$env:PG_PASSWORD="mQIAEdnVXzPLszj17Vp93tqceDNEYaEF7ywnuBFyRTDO5A7mJEyYel5zz266fVIp"
 $env:PG_PORT="5432"</t>
   </si>
 </sst>
@@ -40649,7 +40649,7 @@
         <v>59086154</v>
       </c>
     </row>
-    <row r="17" spans="6:6" ht="72.900000000000006" x14ac:dyDescent="0.4">
+    <row r="17" spans="6:6" ht="87.45" x14ac:dyDescent="0.4">
       <c r="F17" s="1" t="s">
         <v>77</v>
       </c>
